--- a/outputs/city_hotel_fake_reservations.xlsx
+++ b/outputs/city_hotel_fake_reservations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Reservations" sheetId="1" r:id="Re88e26f55d3641ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Reservations" sheetId="1" r:id="R20bf718527984e22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -615,7 +615,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E2" s="30" t="str">
         <x:v>August</x:v>
@@ -700,7 +700,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D3" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E3" s="30" t="str">
         <x:v>August</x:v>
@@ -785,13 +785,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D4" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E4" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F4" s="30" t="str">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G4" s="30" t="str">
         <x:v>3</x:v>
@@ -870,13 +870,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E5" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F5" s="30" t="str">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G5" s="30" t="str">
         <x:v>4</x:v>
@@ -955,13 +955,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E6" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F6" s="30" t="str">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G6" s="30" t="str">
         <x:v>5</x:v>
@@ -1040,13 +1040,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E7" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F7" s="30" t="str">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G7" s="30" t="str">
         <x:v>6</x:v>
@@ -1125,7 +1125,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D8" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E8" s="30" t="str">
         <x:v>August</x:v>
@@ -1210,7 +1210,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E9" s="30" t="str">
         <x:v>August</x:v>
@@ -1295,7 +1295,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E10" s="30" t="str">
         <x:v>August</x:v>
@@ -1380,13 +1380,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E11" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F11" s="30" t="str">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G11" s="30" t="str">
         <x:v>10</x:v>
@@ -1462,25 +1462,25 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C12" s="30" t="str">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E12" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F12" s="30" t="str">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="30" t="str">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H12" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J12" s="30" t="str">
         <x:v>2</x:v>
@@ -1498,10 +1498,10 @@
         <x:v>PRT</x:v>
       </x:c>
       <x:c r="O12" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P12" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q12" s="30" t="str">
         <x:v>0</x:v>
@@ -1510,20 +1510,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S12" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T12" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U12" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V12" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W12" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W12" s="30" t="str"/>
       <x:c r="X12" s="30" t="str"/>
       <x:c r="Y12" s="30" t="str">
         <x:v>0</x:v>
@@ -1532,13 +1530,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA12" s="30" t="str">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="AB12" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC12" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1549,16 +1547,16 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C13" s="30" t="str">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D13" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E13" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F13" s="30" t="str">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G13" s="30" t="str">
         <x:v>12</x:v>
@@ -1567,7 +1565,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J13" s="30" t="str">
         <x:v>2</x:v>
@@ -1585,10 +1583,10 @@
         <x:v>GBR</x:v>
       </x:c>
       <x:c r="O13" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P13" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q13" s="30" t="str">
         <x:v>0</x:v>
@@ -1597,20 +1595,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S13" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T13" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U13" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V13" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W13" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W13" s="30" t="str"/>
       <x:c r="X13" s="30" t="str"/>
       <x:c r="Y13" s="30" t="str">
         <x:v>0</x:v>
@@ -1619,13 +1615,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA13" s="30" t="str">
-        <x:v>109</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="AB13" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC13" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1636,31 +1632,31 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C14" s="30" t="str">
-        <x:v>63</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D14" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E14" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F14" s="30" t="str">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G14" s="30" t="str">
         <x:v>13</x:v>
       </x:c>
       <x:c r="H14" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J14" s="30" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K14" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L14" s="30" t="str">
         <x:v>0</x:v>
@@ -1672,19 +1668,19 @@
         <x:v>FRA</x:v>
       </x:c>
       <x:c r="O14" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P14" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q14" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R14" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="S14" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T14" s="30" t="str">
         <x:v>D</x:v>
@@ -1695,9 +1691,7 @@
       <x:c r="V14" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W14" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W14" s="30" t="str"/>
       <x:c r="X14" s="30" t="str"/>
       <x:c r="Y14" s="30" t="str">
         <x:v>0</x:v>
@@ -1706,13 +1700,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA14" s="30" t="str">
-        <x:v>113</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="AB14" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC14" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1723,10 +1717,10 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C15" s="30" t="str">
-        <x:v>72</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D15" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E15" s="30" t="str">
         <x:v>August</x:v>
@@ -1741,7 +1735,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J15" s="30" t="str">
         <x:v>2</x:v>
@@ -1759,10 +1753,10 @@
         <x:v>ESP</x:v>
       </x:c>
       <x:c r="O15" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P15" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q15" s="30" t="str">
         <x:v>0</x:v>
@@ -1771,20 +1765,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S15" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T15" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U15" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V15" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W15" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W15" s="30" t="str"/>
       <x:c r="X15" s="30" t="str"/>
       <x:c r="Y15" s="30" t="str">
         <x:v>0</x:v>
@@ -1793,13 +1785,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA15" s="30" t="str">
-        <x:v>117</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AB15" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC15" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1810,10 +1802,10 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C16" s="30" t="str">
-        <x:v>81</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D16" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E16" s="30" t="str">
         <x:v>August</x:v>
@@ -1825,10 +1817,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="30" t="str">
         <x:v>1</x:v>
@@ -1846,10 +1838,10 @@
         <x:v>DEU</x:v>
       </x:c>
       <x:c r="O16" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P16" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q16" s="30" t="str">
         <x:v>0</x:v>
@@ -1858,20 +1850,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S16" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T16" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U16" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V16" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W16" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W16" s="30" t="str"/>
       <x:c r="X16" s="30" t="str"/>
       <x:c r="Y16" s="30" t="str">
         <x:v>0</x:v>
@@ -1880,13 +1870,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA16" s="30" t="str">
-        <x:v>121</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="AB16" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC16" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1897,10 +1887,10 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C17" s="30" t="str">
-        <x:v>90</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E17" s="30" t="str">
         <x:v>August</x:v>
@@ -1915,13 +1905,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J17" s="30" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K17" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L17" s="30" t="str">
         <x:v>0</x:v>
@@ -1933,19 +1923,19 @@
         <x:v>PRT</x:v>
       </x:c>
       <x:c r="O17" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P17" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q17" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R17" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="S17" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T17" s="30" t="str">
         <x:v>A</x:v>
@@ -1956,9 +1946,7 @@
       <x:c r="V17" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W17" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W17" s="30" t="str"/>
       <x:c r="X17" s="30" t="str"/>
       <x:c r="Y17" s="30" t="str">
         <x:v>0</x:v>
@@ -1967,13 +1955,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA17" s="30" t="str">
-        <x:v>125</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="AB17" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC17" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1984,25 +1972,25 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C18" s="30" t="str">
-        <x:v>99</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D18" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E18" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F18" s="30" t="str">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G18" s="30" t="str">
         <x:v>17</x:v>
       </x:c>
       <x:c r="H18" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J18" s="30" t="str">
         <x:v>2</x:v>
@@ -2020,10 +2008,10 @@
         <x:v>GBR</x:v>
       </x:c>
       <x:c r="O18" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P18" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q18" s="30" t="str">
         <x:v>0</x:v>
@@ -2032,20 +2020,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S18" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T18" s="30" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="U18" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V18" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W18" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W18" s="30" t="str"/>
       <x:c r="X18" s="30" t="str"/>
       <x:c r="Y18" s="30" t="str">
         <x:v>0</x:v>
@@ -2054,13 +2040,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA18" s="30" t="str">
-        <x:v>129</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AB18" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC18" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2071,16 +2057,16 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C19" s="30" t="str">
-        <x:v>108</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D19" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E19" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F19" s="30" t="str">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G19" s="30" t="str">
         <x:v>18</x:v>
@@ -2089,7 +2075,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J19" s="30" t="str">
         <x:v>2</x:v>
@@ -2107,10 +2093,10 @@
         <x:v>FRA</x:v>
       </x:c>
       <x:c r="O19" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P19" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q19" s="30" t="str">
         <x:v>0</x:v>
@@ -2119,20 +2105,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S19" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T19" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U19" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V19" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W19" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W19" s="30" t="str"/>
       <x:c r="X19" s="30" t="str"/>
       <x:c r="Y19" s="30" t="str">
         <x:v>0</x:v>
@@ -2141,13 +2125,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA19" s="30" t="str">
-        <x:v>133</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="AB19" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC19" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2158,31 +2142,31 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C20" s="30" t="str">
-        <x:v>117</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D20" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E20" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F20" s="30" t="str">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G20" s="30" t="str">
         <x:v>19</x:v>
       </x:c>
       <x:c r="H20" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J20" s="30" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K20" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L20" s="30" t="str">
         <x:v>0</x:v>
@@ -2194,19 +2178,19 @@
         <x:v>ESP</x:v>
       </x:c>
       <x:c r="O20" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P20" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q20" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R20" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="S20" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T20" s="30" t="str">
         <x:v>A</x:v>
@@ -2217,9 +2201,7 @@
       <x:c r="V20" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W20" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W20" s="30" t="str"/>
       <x:c r="X20" s="30" t="str"/>
       <x:c r="Y20" s="30" t="str">
         <x:v>0</x:v>
@@ -2228,13 +2210,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA20" s="30" t="str">
-        <x:v>137</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="AB20" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC20" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2245,16 +2227,16 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C21" s="30" t="str">
-        <x:v>126</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E21" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F21" s="30" t="str">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G21" s="30" t="str">
         <x:v>20</x:v>
@@ -2263,7 +2245,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J21" s="30" t="str">
         <x:v>2</x:v>
@@ -2281,10 +2263,10 @@
         <x:v>DEU</x:v>
       </x:c>
       <x:c r="O21" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P21" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q21" s="30" t="str">
         <x:v>0</x:v>
@@ -2293,20 +2275,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S21" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T21" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U21" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V21" s="30" t="str">
         <x:v>No Deposit</x:v>
       </x:c>
-      <x:c r="W21" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="W21" s="30" t="str"/>
       <x:c r="X21" s="30" t="str"/>
       <x:c r="Y21" s="30" t="str">
         <x:v>0</x:v>
@@ -2315,13 +2295,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA21" s="30" t="str">
-        <x:v>141</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="AB21" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC21" s="34" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2332,10 +2312,10 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C22" s="30" t="str">
-        <x:v>180</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E22" s="30" t="str">
         <x:v>August</x:v>
@@ -2347,10 +2327,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H22" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J22" s="30" t="str">
         <x:v>2</x:v>
@@ -2368,32 +2348,30 @@
         <x:v>PRT</x:v>
       </x:c>
       <x:c r="O22" s="12" t="str">
-        <x:v>Groups</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P22" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q22" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R22" s="30" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S22" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T22" s="30" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="U22" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V22" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W22" s="30" t="str">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W22" s="30" t="str"/>
       <x:c r="X22" s="30" t="str"/>
       <x:c r="Y22" s="30" t="str">
         <x:v>0</x:v>
@@ -2402,13 +2380,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA22" s="30" t="str">
-        <x:v>145</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="AB22" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC22" s="34" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2419,10 +2397,10 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C23" s="30" t="str">
-        <x:v>198</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D23" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E23" s="30" t="str">
         <x:v>August</x:v>
@@ -2434,16 +2412,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H23" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J23" s="30" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K23" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L23" s="30" t="str">
         <x:v>0</x:v>
@@ -2455,32 +2433,30 @@
         <x:v>GBR</x:v>
       </x:c>
       <x:c r="O23" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P23" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q23" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R23" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S23" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T23" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U23" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V23" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W23" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W23" s="30" t="str"/>
       <x:c r="X23" s="30" t="str"/>
       <x:c r="Y23" s="30" t="str">
         <x:v>0</x:v>
@@ -2489,13 +2465,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA23" s="30" t="str">
-        <x:v>152</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="AB23" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC23" s="34" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2506,10 +2482,10 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C24" s="30" t="str">
-        <x:v>216</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D24" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E24" s="30" t="str">
         <x:v>August</x:v>
@@ -2521,10 +2497,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H24" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J24" s="30" t="str">
         <x:v>2</x:v>
@@ -2542,32 +2518,30 @@
         <x:v>FRA</x:v>
       </x:c>
       <x:c r="O24" s="12" t="str">
-        <x:v>Groups</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P24" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q24" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R24" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S24" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T24" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U24" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V24" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W24" s="30" t="str">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W24" s="30" t="str"/>
       <x:c r="X24" s="30" t="str"/>
       <x:c r="Y24" s="30" t="str">
         <x:v>0</x:v>
@@ -2576,13 +2550,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA24" s="30" t="str">
-        <x:v>159</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="AB24" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC24" s="34" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2593,25 +2567,25 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C25" s="30" t="str">
-        <x:v>234</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D25" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E25" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F25" s="30" t="str">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G25" s="30" t="str">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H25" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I25" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J25" s="30" t="str">
         <x:v>2</x:v>
@@ -2629,32 +2603,30 @@
         <x:v>ESP</x:v>
       </x:c>
       <x:c r="O25" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P25" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q25" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R25" s="30" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S25" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T25" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U25" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V25" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W25" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W25" s="30" t="str"/>
       <x:c r="X25" s="30" t="str"/>
       <x:c r="Y25" s="30" t="str">
         <x:v>0</x:v>
@@ -2663,13 +2635,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA25" s="30" t="str">
-        <x:v>166</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="AB25" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC25" s="34" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2680,31 +2652,31 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C26" s="30" t="str">
-        <x:v>252</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D26" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E26" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F26" s="30" t="str">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G26" s="30" t="str">
         <x:v>25</x:v>
       </x:c>
       <x:c r="H26" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I26" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J26" s="30" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K26" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L26" s="30" t="str">
         <x:v>0</x:v>
@@ -2716,32 +2688,30 @@
         <x:v>DEU</x:v>
       </x:c>
       <x:c r="O26" s="12" t="str">
-        <x:v>Groups</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P26" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q26" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R26" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S26" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T26" s="30" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="U26" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V26" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W26" s="30" t="str">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W26" s="30" t="str"/>
       <x:c r="X26" s="30" t="str"/>
       <x:c r="Y26" s="30" t="str">
         <x:v>0</x:v>
@@ -2750,13 +2720,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA26" s="30" t="str">
-        <x:v>173</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="AB26" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC26" s="34" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2767,25 +2737,25 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C27" s="30" t="str">
-        <x:v>270</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D27" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E27" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F27" s="30" t="str">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G27" s="30" t="str">
         <x:v>26</x:v>
       </x:c>
       <x:c r="H27" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J27" s="30" t="str">
         <x:v>2</x:v>
@@ -2803,32 +2773,30 @@
         <x:v>PRT</x:v>
       </x:c>
       <x:c r="O27" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P27" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q27" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R27" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S27" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T27" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U27" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V27" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W27" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W27" s="30" t="str"/>
       <x:c r="X27" s="30" t="str"/>
       <x:c r="Y27" s="30" t="str">
         <x:v>0</x:v>
@@ -2837,13 +2805,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA27" s="30" t="str">
-        <x:v>180</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AB27" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC27" s="34" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2854,25 +2822,25 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C28" s="30" t="str">
-        <x:v>288</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D28" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E28" s="30" t="str">
         <x:v>August</x:v>
       </x:c>
       <x:c r="F28" s="30" t="str">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G28" s="30" t="str">
         <x:v>27</x:v>
       </x:c>
       <x:c r="H28" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I28" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J28" s="30" t="str">
         <x:v>2</x:v>
@@ -2890,32 +2858,30 @@
         <x:v>GBR</x:v>
       </x:c>
       <x:c r="O28" s="12" t="str">
-        <x:v>Groups</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P28" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q28" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R28" s="30" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S28" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T28" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U28" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V28" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W28" s="30" t="str">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W28" s="30" t="str"/>
       <x:c r="X28" s="30" t="str"/>
       <x:c r="Y28" s="30" t="str">
         <x:v>0</x:v>
@@ -2924,13 +2890,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA28" s="30" t="str">
-        <x:v>187</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="AB28" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC28" s="34" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2941,10 +2907,10 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C29" s="30" t="str">
-        <x:v>306</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D29" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E29" s="30" t="str">
         <x:v>August</x:v>
@@ -2956,16 +2922,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H29" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J29" s="30" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K29" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L29" s="30" t="str">
         <x:v>0</x:v>
@@ -2977,32 +2943,30 @@
         <x:v>FRA</x:v>
       </x:c>
       <x:c r="O29" s="12" t="str">
-        <x:v>Online TA</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P29" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q29" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R29" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S29" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T29" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="U29" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V29" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W29" s="30" t="str">
-        <x:v>9</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W29" s="30" t="str"/>
       <x:c r="X29" s="30" t="str"/>
       <x:c r="Y29" s="30" t="str">
         <x:v>0</x:v>
@@ -3011,13 +2975,13 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA29" s="30" t="str">
-        <x:v>194</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="AB29" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC29" s="34" t="str">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3028,10 +2992,10 @@
         <x:v>City Hotel</x:v>
       </x:c>
       <x:c r="C30" s="30" t="str">
-        <x:v>324</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D30" s="30" t="str">
-        <x:v>2017</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="E30" s="30" t="str">
         <x:v>August</x:v>
@@ -3043,10 +3007,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H30" s="30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="30" t="str">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J30" s="30" t="str">
         <x:v>1</x:v>
@@ -3064,32 +3028,30 @@
         <x:v>ESP</x:v>
       </x:c>
       <x:c r="O30" s="12" t="str">
-        <x:v>Groups</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="P30" s="12" t="str">
-        <x:v>TA/TO</x:v>
+        <x:v>Direct</x:v>
       </x:c>
       <x:c r="Q30" s="30" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R30" s="30" t="str">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S30" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T30" s="30" t="str">
         <x:v>D</x:v>
       </x:c>
       <x:c r="U30" s="30" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V30" s="30" t="str">
-        <x:v>Non Refund</x:v>
-      </x:c>
-      <x:c r="W30" s="30" t="str">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W30" s="30" t="str"/>
       <x:c r="X30" s="30" t="str"/>
       <x:c r="Y30" s="30" t="str">
         <x:v>0</x:v>
@@ -3098,99 +3060,6179 @@
         <x:v>Transient</x:v>
       </x:c>
       <x:c r="AA30" s="30" t="str">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="AB30" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC30" s="34" t="str">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="26" t="str">
+        <x:v>TEST-030</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="str">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D31" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E31" s="30" t="str">
+        <x:v>August</x:v>
+      </x:c>
+      <x:c r="F31" s="30" t="str">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="str">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H31" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J31" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K31" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L31" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M31" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N31" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O31" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="P31" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="Q31" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R31" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S31" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T31" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U31" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V31" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W31" s="30" t="str"/>
+      <x:c r="X31" s="30" t="str"/>
+      <x:c r="Y31" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z31" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA31" s="30" t="str">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="AB31" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC31" s="34" t="str">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="26" t="str">
+        <x:v>TEST-031</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="str">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D32" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E32" s="30" t="str">
+        <x:v>August</x:v>
+      </x:c>
+      <x:c r="F32" s="30" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="str">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H32" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I32" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J32" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K32" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L32" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M32" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N32" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O32" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="P32" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="Q32" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R32" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S32" s="30" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T32" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U32" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V32" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W32" s="30" t="str"/>
+      <x:c r="X32" s="30" t="str"/>
+      <x:c r="Y32" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z32" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA32" s="30" t="str">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="AB32" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC32" s="34" t="str">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="26" t="str">
+        <x:v>TEST-032</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="str">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D33" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E33" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F33" s="30" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G33" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I33" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J33" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K33" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L33" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M33" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N33" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O33" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="P33" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="Q33" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R33" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S33" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T33" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U33" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V33" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W33" s="30" t="str"/>
+      <x:c r="X33" s="30" t="str"/>
+      <x:c r="Y33" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z33" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA33" s="30" t="str">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AB33" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC33" s="34" t="str">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="26" t="str">
+        <x:v>TEST-033</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="str">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D34" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E34" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F34" s="30" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H34" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I34" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J34" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K34" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N34" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O34" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="P34" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="Q34" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R34" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S34" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T34" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U34" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V34" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W34" s="30" t="str"/>
+      <x:c r="X34" s="30" t="str"/>
+      <x:c r="Y34" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z34" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA34" s="30" t="str">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="AB34" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC34" s="34" t="str">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="26" t="str">
+        <x:v>TEST-034</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="str">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D35" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E35" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F35" s="30" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G35" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H35" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I35" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J35" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K35" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L35" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N35" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O35" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="P35" s="12" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="Q35" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R35" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S35" s="30" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T35" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U35" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V35" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W35" s="30" t="str"/>
+      <x:c r="X35" s="30" t="str"/>
+      <x:c r="Y35" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z35" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA35" s="30" t="str">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="AB35" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC35" s="34" t="str">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="26" t="str">
+        <x:v>TEST-035</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D36" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E36" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F36" s="30" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H36" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J36" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K36" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N36" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O36" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P36" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q36" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R36" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S36" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T36" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U36" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V36" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W36" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X36" s="30" t="str"/>
+      <x:c r="Y36" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z36" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA36" s="30" t="str">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="AB36" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC36" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="26" t="str">
+        <x:v>TEST-036</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="str">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D37" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E37" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F37" s="30" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G37" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H37" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I37" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J37" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K37" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N37" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O37" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P37" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q37" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R37" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S37" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T37" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U37" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V37" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W37" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X37" s="30" t="str"/>
+      <x:c r="Y37" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z37" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA37" s="30" t="str">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="AB37" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC37" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="26" t="str">
+        <x:v>TEST-037</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C38" s="30" t="str">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D38" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E38" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F38" s="30" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J38" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N38" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O38" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P38" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T38" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V38" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W38" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X38" s="30" t="str"/>
+      <x:c r="Y38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z38" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA38" s="30" t="str">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="AB38" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC38" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="26" t="str">
+        <x:v>TEST-038</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C39" s="30" t="str">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D39" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E39" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F39" s="30" t="str">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G39" s="30" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H39" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I39" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J39" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K39" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L39" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N39" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O39" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P39" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q39" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R39" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S39" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T39" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U39" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V39" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W39" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X39" s="30" t="str"/>
+      <x:c r="Y39" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z39" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA39" s="30" t="str">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="AB39" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC39" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="26" t="str">
+        <x:v>TEST-039</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C40" s="30" t="str">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D40" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E40" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F40" s="30" t="str">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G40" s="30" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J40" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N40" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O40" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P40" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T40" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V40" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W40" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X40" s="30" t="str"/>
+      <x:c r="Y40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z40" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA40" s="30" t="str">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="AB40" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC40" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="26" t="str">
+        <x:v>TEST-040</x:v>
+      </x:c>
+      <x:c r="B41" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C41" s="30" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D41" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E41" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F41" s="30" t="str">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G41" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H41" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I41" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K41" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L41" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M41" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N41" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O41" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P41" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q41" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R41" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S41" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T41" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U41" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V41" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W41" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X41" s="30" t="str"/>
+      <x:c r="Y41" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z41" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA41" s="30" t="str">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AB41" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC41" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="26" t="str">
+        <x:v>TEST-041</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C42" s="30" t="str">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D42" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E42" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F42" s="30" t="str">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G42" s="30" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H42" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K42" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M42" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N42" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O42" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P42" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q42" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R42" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S42" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T42" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U42" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V42" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W42" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X42" s="30" t="str"/>
+      <x:c r="Y42" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z42" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA42" s="30" t="str">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="AB42" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC42" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="26" t="str">
+        <x:v>TEST-042</x:v>
+      </x:c>
+      <x:c r="B43" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C43" s="30" t="str">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D43" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E43" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F43" s="30" t="str">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G43" s="30" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H43" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I43" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J43" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K43" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L43" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M43" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N43" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O43" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P43" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q43" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R43" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S43" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T43" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U43" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V43" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W43" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X43" s="30" t="str"/>
+      <x:c r="Y43" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z43" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA43" s="30" t="str">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="AB43" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC43" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="26" t="str">
+        <x:v>TEST-043</x:v>
+      </x:c>
+      <x:c r="B44" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C44" s="30" t="str">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D44" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E44" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F44" s="30" t="str">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G44" s="30" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M44" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N44" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O44" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P44" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T44" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V44" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W44" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X44" s="30" t="str"/>
+      <x:c r="Y44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z44" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA44" s="30" t="str">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="AB44" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC44" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="26" t="str">
+        <x:v>TEST-044</x:v>
+      </x:c>
+      <x:c r="B45" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C45" s="30" t="str">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D45" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E45" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F45" s="30" t="str">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G45" s="30" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H45" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I45" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K45" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L45" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M45" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N45" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O45" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P45" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q45" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R45" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S45" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T45" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U45" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V45" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W45" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X45" s="30" t="str"/>
+      <x:c r="Y45" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z45" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA45" s="30" t="str">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="AB45" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC45" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="26" t="str">
+        <x:v>TEST-045</x:v>
+      </x:c>
+      <x:c r="B46" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C46" s="30" t="str">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D46" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E46" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F46" s="30" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G46" s="30" t="str">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I46" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J46" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M46" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N46" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O46" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P46" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T46" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V46" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W46" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X46" s="30" t="str"/>
+      <x:c r="Y46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z46" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA46" s="30" t="str">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="AB46" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC46" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="26" t="str">
+        <x:v>TEST-046</x:v>
+      </x:c>
+      <x:c r="B47" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="str">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D47" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E47" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F47" s="30" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G47" s="30" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H47" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I47" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J47" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K47" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L47" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M47" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N47" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O47" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P47" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q47" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R47" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S47" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T47" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U47" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V47" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W47" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X47" s="30" t="str"/>
+      <x:c r="Y47" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z47" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA47" s="30" t="str">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="AB47" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC47" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="26" t="str">
+        <x:v>TEST-047</x:v>
+      </x:c>
+      <x:c r="B48" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="str">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D48" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E48" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F48" s="30" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G48" s="30" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H48" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I48" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J48" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K48" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L48" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M48" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N48" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O48" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P48" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q48" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R48" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S48" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T48" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U48" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V48" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W48" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X48" s="30" t="str"/>
+      <x:c r="Y48" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z48" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA48" s="30" t="str">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="AB48" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC48" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="26" t="str">
+        <x:v>TEST-048</x:v>
+      </x:c>
+      <x:c r="B49" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="str">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D49" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E49" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F49" s="30" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G49" s="30" t="str">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H49" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I49" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J49" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K49" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M49" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N49" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O49" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P49" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q49" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R49" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S49" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T49" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U49" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V49" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W49" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X49" s="30" t="str"/>
+      <x:c r="Y49" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z49" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA49" s="30" t="str">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="AB49" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC49" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="26" t="str">
+        <x:v>TEST-049</x:v>
+      </x:c>
+      <x:c r="B50" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="str">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D50" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E50" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F50" s="30" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G50" s="30" t="str">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I50" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J50" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M50" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N50" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O50" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P50" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T50" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V50" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W50" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X50" s="30" t="str"/>
+      <x:c r="Y50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z50" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA50" s="30" t="str">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="AB50" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC50" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="26" t="str">
+        <x:v>TEST-050</x:v>
+      </x:c>
+      <x:c r="B51" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="str">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D51" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E51" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F51" s="30" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G51" s="30" t="str">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H51" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I51" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J51" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K51" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L51" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M51" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N51" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O51" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P51" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q51" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R51" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S51" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T51" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U51" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V51" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W51" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X51" s="30" t="str"/>
+      <x:c r="Y51" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z51" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA51" s="30" t="str">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AB51" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC51" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="26" t="str">
+        <x:v>TEST-051</x:v>
+      </x:c>
+      <x:c r="B52" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="str">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D52" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E52" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F52" s="30" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G52" s="30" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I52" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J52" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M52" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N52" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O52" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P52" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T52" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V52" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W52" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X52" s="30" t="str"/>
+      <x:c r="Y52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z52" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA52" s="30" t="str">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="AB52" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC52" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="26" t="str">
+        <x:v>TEST-052</x:v>
+      </x:c>
+      <x:c r="B53" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C53" s="30" t="str">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D53" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E53" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F53" s="30" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G53" s="30" t="str">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H53" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I53" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J53" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K53" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L53" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M53" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N53" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O53" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P53" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q53" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R53" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S53" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T53" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U53" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V53" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W53" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X53" s="30" t="str"/>
+      <x:c r="Y53" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z53" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA53" s="30" t="str">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="AB53" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC53" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="26" t="str">
+        <x:v>TEST-053</x:v>
+      </x:c>
+      <x:c r="B54" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C54" s="30" t="str">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D54" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E54" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F54" s="30" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G54" s="30" t="str">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H54" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I54" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J54" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K54" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L54" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M54" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N54" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O54" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P54" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q54" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R54" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S54" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T54" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U54" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V54" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W54" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X54" s="30" t="str"/>
+      <x:c r="Y54" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z54" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA54" s="30" t="str">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="AB54" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC54" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="26" t="str">
+        <x:v>TEST-054</x:v>
+      </x:c>
+      <x:c r="B55" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C55" s="30" t="str">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D55" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E55" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F55" s="30" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G55" s="30" t="str">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H55" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I55" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J55" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K55" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L55" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M55" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N55" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O55" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P55" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q55" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R55" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S55" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T55" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U55" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V55" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W55" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X55" s="30" t="str"/>
+      <x:c r="Y55" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z55" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA55" s="30" t="str">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="AB55" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC55" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="26" t="str">
+        <x:v>TEST-055</x:v>
+      </x:c>
+      <x:c r="B56" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C56" s="30" t="str">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D56" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E56" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F56" s="30" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G56" s="30" t="str">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I56" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J56" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M56" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N56" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O56" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P56" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T56" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V56" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W56" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X56" s="30" t="str"/>
+      <x:c r="Y56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z56" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA56" s="30" t="str">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AB56" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC56" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="26" t="str">
+        <x:v>TEST-056</x:v>
+      </x:c>
+      <x:c r="B57" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C57" s="30" t="str">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D57" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E57" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F57" s="30" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G57" s="30" t="str">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H57" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I57" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J57" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K57" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L57" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M57" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N57" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O57" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P57" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q57" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R57" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S57" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T57" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U57" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V57" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W57" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X57" s="30" t="str"/>
+      <x:c r="Y57" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z57" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA57" s="30" t="str">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="AB57" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC57" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="26" t="str">
+        <x:v>TEST-057</x:v>
+      </x:c>
+      <x:c r="B58" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C58" s="30" t="str">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D58" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E58" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F58" s="30" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G58" s="30" t="str">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I58" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J58" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M58" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N58" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O58" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P58" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T58" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V58" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W58" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X58" s="30" t="str"/>
+      <x:c r="Y58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z58" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA58" s="30" t="str">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="AB58" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC58" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="26" t="str">
+        <x:v>TEST-058</x:v>
+      </x:c>
+      <x:c r="B59" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C59" s="30" t="str">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D59" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E59" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F59" s="30" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G59" s="30" t="str">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H59" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I59" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J59" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K59" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L59" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M59" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N59" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O59" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P59" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q59" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R59" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S59" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T59" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U59" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V59" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W59" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X59" s="30" t="str"/>
+      <x:c r="Y59" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z59" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA59" s="30" t="str">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="AB59" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC59" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="26" t="str">
+        <x:v>TEST-059</x:v>
+      </x:c>
+      <x:c r="B60" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C60" s="30" t="str">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D60" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E60" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F60" s="30" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G60" s="30" t="str">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H60" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I60" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J60" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K60" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L60" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M60" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N60" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O60" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P60" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q60" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R60" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S60" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T60" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U60" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V60" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W60" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X60" s="30" t="str"/>
+      <x:c r="Y60" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z60" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA60" s="30" t="str">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="AB60" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC60" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="26" t="str">
+        <x:v>TEST-060</x:v>
+      </x:c>
+      <x:c r="B61" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C61" s="30" t="str">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D61" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E61" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F61" s="30" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G61" s="30" t="str">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H61" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I61" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J61" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K61" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L61" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M61" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N61" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O61" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P61" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q61" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R61" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S61" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T61" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U61" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V61" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W61" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X61" s="30" t="str"/>
+      <x:c r="Y61" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z61" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA61" s="30" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="AB61" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC61" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="26" t="str">
+        <x:v>TEST-061</x:v>
+      </x:c>
+      <x:c r="B62" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C62" s="30" t="str">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D62" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E62" s="30" t="str">
+        <x:v>September</x:v>
+      </x:c>
+      <x:c r="F62" s="30" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G62" s="30" t="str">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I62" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J62" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M62" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N62" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O62" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P62" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T62" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V62" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W62" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X62" s="30" t="str"/>
+      <x:c r="Y62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z62" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA62" s="30" t="str">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="AB62" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC62" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="26" t="str">
+        <x:v>TEST-062</x:v>
+      </x:c>
+      <x:c r="B63" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C63" s="30" t="str">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D63" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E63" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F63" s="30" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G63" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H63" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I63" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J63" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K63" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M63" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N63" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O63" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P63" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q63" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R63" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S63" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T63" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U63" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V63" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W63" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X63" s="30" t="str"/>
+      <x:c r="Y63" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z63" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA63" s="30" t="str">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="AB63" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC63" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="26" t="str">
+        <x:v>TEST-063</x:v>
+      </x:c>
+      <x:c r="B64" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C64" s="30" t="str">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D64" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E64" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F64" s="30" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G64" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I64" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J64" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M64" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N64" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O64" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P64" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T64" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V64" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W64" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X64" s="30" t="str"/>
+      <x:c r="Y64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z64" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA64" s="30" t="str">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="AB64" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC64" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="26" t="str">
+        <x:v>TEST-064</x:v>
+      </x:c>
+      <x:c r="B65" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C65" s="30" t="str">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D65" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E65" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F65" s="30" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G65" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H65" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I65" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J65" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K65" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L65" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M65" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N65" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O65" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P65" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q65" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R65" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S65" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T65" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U65" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V65" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W65" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X65" s="30" t="str"/>
+      <x:c r="Y65" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z65" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA65" s="30" t="str">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="AB65" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC65" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="26" t="str">
+        <x:v>TEST-065</x:v>
+      </x:c>
+      <x:c r="B66" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C66" s="30" t="str">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D66" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E66" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F66" s="30" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G66" s="30" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H66" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I66" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J66" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K66" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L66" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M66" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N66" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O66" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P66" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q66" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R66" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S66" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T66" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U66" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V66" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W66" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X66" s="30" t="str"/>
+      <x:c r="Y66" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z66" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA66" s="30" t="str">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="AB66" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC66" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="26" t="str">
+        <x:v>TEST-066</x:v>
+      </x:c>
+      <x:c r="B67" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C67" s="30" t="str">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D67" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E67" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F67" s="30" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G67" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H67" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I67" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J67" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K67" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L67" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M67" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N67" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O67" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P67" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q67" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R67" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S67" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T67" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U67" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V67" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W67" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X67" s="30" t="str"/>
+      <x:c r="Y67" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z67" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA67" s="30" t="str">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="AB67" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC67" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="26" t="str">
+        <x:v>TEST-067</x:v>
+      </x:c>
+      <x:c r="B68" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C68" s="30" t="str">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D68" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E68" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F68" s="30" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G68" s="30" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I68" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J68" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M68" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N68" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O68" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P68" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T68" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V68" s="30" t="str">
+        <x:v>No Deposit</x:v>
+      </x:c>
+      <x:c r="W68" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X68" s="30" t="str"/>
+      <x:c r="Y68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z68" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA68" s="30" t="str">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="AB30" s="30" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC30" s="34" t="str">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="27" t="str">
-        <x:v>TEST-030</x:v>
-      </x:c>
-      <x:c r="B31" s="15" t="str">
-        <x:v>City Hotel</x:v>
-      </x:c>
-      <x:c r="C31" s="31" t="str">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="D31" s="31" t="str">
-        <x:v>2017</x:v>
-      </x:c>
-      <x:c r="E31" s="31" t="str">
-        <x:v>August</x:v>
-      </x:c>
-      <x:c r="F31" s="31" t="str">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G31" s="31" t="str">
+      <x:c r="AB68" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC68" s="34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="26" t="str">
+        <x:v>TEST-068</x:v>
+      </x:c>
+      <x:c r="B69" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C69" s="30" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D69" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E69" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F69" s="30" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G69" s="30" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H69" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I69" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J69" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K69" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L69" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M69" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N69" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O69" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P69" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q69" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R69" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S69" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T69" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U69" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V69" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W69" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X69" s="30" t="str"/>
+      <x:c r="Y69" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z69" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA69" s="30" t="str">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="AB69" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC69" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="26" t="str">
+        <x:v>TEST-069</x:v>
+      </x:c>
+      <x:c r="B70" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C70" s="30" t="str">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D70" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E70" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F70" s="30" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G70" s="30" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H70" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I70" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J70" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K70" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L70" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M70" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N70" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O70" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P70" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q70" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R70" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S70" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T70" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U70" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V70" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W70" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X70" s="30" t="str"/>
+      <x:c r="Y70" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z70" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA70" s="30" t="str">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AB70" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC70" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="26" t="str">
+        <x:v>TEST-070</x:v>
+      </x:c>
+      <x:c r="B71" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C71" s="30" t="str">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D71" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E71" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F71" s="30" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G71" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H71" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I71" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J71" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K71" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L71" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M71" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N71" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O71" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P71" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q71" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R71" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S71" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T71" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U71" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V71" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W71" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X71" s="30" t="str"/>
+      <x:c r="Y71" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z71" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA71" s="30" t="str">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="AB71" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC71" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="26" t="str">
+        <x:v>TEST-071</x:v>
+      </x:c>
+      <x:c r="B72" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C72" s="30" t="str">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D72" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E72" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F72" s="30" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G72" s="30" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H72" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I72" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J72" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K72" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L72" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M72" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N72" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O72" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P72" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q72" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R72" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S72" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T72" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U72" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V72" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W72" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X72" s="30" t="str"/>
+      <x:c r="Y72" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z72" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA72" s="30" t="str">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="AB72" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC72" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="26" t="str">
+        <x:v>TEST-072</x:v>
+      </x:c>
+      <x:c r="B73" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C73" s="30" t="str">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D73" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E73" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F73" s="30" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G73" s="30" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H73" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I73" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J73" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K73" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L73" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M73" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N73" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O73" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P73" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q73" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R73" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S73" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T73" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U73" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V73" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W73" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X73" s="30" t="str"/>
+      <x:c r="Y73" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z73" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA73" s="30" t="str">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AB73" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC73" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="26" t="str">
+        <x:v>TEST-073</x:v>
+      </x:c>
+      <x:c r="B74" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C74" s="30" t="str">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D74" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E74" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F74" s="30" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G74" s="30" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H74" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I74" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J74" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K74" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L74" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M74" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N74" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O74" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P74" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q74" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R74" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S74" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T74" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U74" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V74" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W74" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X74" s="30" t="str"/>
+      <x:c r="Y74" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z74" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA74" s="30" t="str">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="AB74" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC74" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="26" t="str">
+        <x:v>TEST-074</x:v>
+      </x:c>
+      <x:c r="B75" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C75" s="30" t="str">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D75" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E75" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F75" s="30" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G75" s="30" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H75" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I75" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J75" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K75" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L75" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M75" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N75" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O75" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P75" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q75" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R75" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S75" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T75" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U75" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V75" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W75" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X75" s="30" t="str"/>
+      <x:c r="Y75" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z75" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA75" s="30" t="str">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="AB75" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC75" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="26" t="str">
+        <x:v>TEST-075</x:v>
+      </x:c>
+      <x:c r="B76" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C76" s="30" t="str">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D76" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E76" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F76" s="30" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G76" s="30" t="str">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H76" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I76" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J76" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K76" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L76" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M76" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N76" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O76" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P76" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q76" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R76" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S76" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T76" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U76" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V76" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W76" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X76" s="30" t="str"/>
+      <x:c r="Y76" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z76" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA76" s="30" t="str">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="AB76" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC76" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="26" t="str">
+        <x:v>TEST-076</x:v>
+      </x:c>
+      <x:c r="B77" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C77" s="30" t="str">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D77" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E77" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F77" s="30" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G77" s="30" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H77" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I77" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J77" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K77" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L77" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M77" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N77" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O77" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P77" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q77" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R77" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S77" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T77" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U77" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V77" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W77" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X77" s="30" t="str"/>
+      <x:c r="Y77" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z77" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA77" s="30" t="str">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="AB77" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC77" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="26" t="str">
+        <x:v>TEST-077</x:v>
+      </x:c>
+      <x:c r="B78" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C78" s="30" t="str">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D78" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E78" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F78" s="30" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G78" s="30" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H78" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I78" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K78" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L78" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M78" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N78" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O78" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P78" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q78" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R78" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S78" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T78" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U78" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V78" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W78" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X78" s="30" t="str"/>
+      <x:c r="Y78" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z78" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA78" s="30" t="str">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="AB78" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC78" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="26" t="str">
+        <x:v>TEST-078</x:v>
+      </x:c>
+      <x:c r="B79" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C79" s="30" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D79" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E79" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F79" s="30" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G79" s="30" t="str">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H79" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I79" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J79" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K79" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L79" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M79" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N79" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O79" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P79" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q79" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R79" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S79" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T79" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U79" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V79" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W79" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X79" s="30" t="str"/>
+      <x:c r="Y79" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z79" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA79" s="30" t="str">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="AB79" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC79" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="26" t="str">
+        <x:v>TEST-079</x:v>
+      </x:c>
+      <x:c r="B80" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C80" s="30" t="str">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="D80" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E80" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F80" s="30" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G80" s="30" t="str">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H80" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I80" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J80" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K80" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L80" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M80" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N80" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O80" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P80" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q80" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R80" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S80" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T80" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U80" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V80" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W80" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X80" s="30" t="str"/>
+      <x:c r="Y80" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z80" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA80" s="30" t="str">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="AB80" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC80" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="26" t="str">
+        <x:v>TEST-080</x:v>
+      </x:c>
+      <x:c r="B81" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C81" s="30" t="str">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="D81" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E81" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F81" s="30" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G81" s="30" t="str">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H81" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I81" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J81" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K81" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L81" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M81" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N81" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O81" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P81" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q81" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R81" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S81" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T81" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U81" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V81" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W81" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X81" s="30" t="str"/>
+      <x:c r="Y81" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z81" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA81" s="30" t="str">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="AB81" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC81" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="26" t="str">
+        <x:v>TEST-081</x:v>
+      </x:c>
+      <x:c r="B82" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C82" s="30" t="str">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="D82" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E82" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F82" s="30" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G82" s="30" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H82" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I82" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J82" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K82" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L82" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M82" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N82" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O82" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P82" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q82" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R82" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S82" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T82" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U82" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V82" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W82" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X82" s="30" t="str"/>
+      <x:c r="Y82" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z82" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA82" s="30" t="str">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="AB82" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC82" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="26" t="str">
+        <x:v>TEST-082</x:v>
+      </x:c>
+      <x:c r="B83" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C83" s="30" t="str">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="D83" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E83" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F83" s="30" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G83" s="30" t="str">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H83" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I83" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J83" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K83" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L83" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M83" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N83" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O83" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P83" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q83" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R83" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S83" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T83" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U83" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V83" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W83" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X83" s="30" t="str"/>
+      <x:c r="Y83" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z83" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA83" s="30" t="str">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="AB83" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC83" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="26" t="str">
+        <x:v>TEST-083</x:v>
+      </x:c>
+      <x:c r="B84" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C84" s="30" t="str">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="D84" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E84" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F84" s="30" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G84" s="30" t="str">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H84" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I84" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J84" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K84" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L84" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M84" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N84" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O84" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P84" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q84" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R84" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S84" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T84" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U84" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V84" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W84" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X84" s="30" t="str"/>
+      <x:c r="Y84" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z84" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA84" s="30" t="str">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="AB84" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC84" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="26" t="str">
+        <x:v>TEST-084</x:v>
+      </x:c>
+      <x:c r="B85" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C85" s="30" t="str">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="D85" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E85" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F85" s="30" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G85" s="30" t="str">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H85" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I85" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J85" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K85" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L85" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M85" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N85" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O85" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P85" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q85" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R85" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S85" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T85" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U85" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V85" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W85" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X85" s="30" t="str"/>
+      <x:c r="Y85" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z85" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA85" s="30" t="str">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="AB85" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC85" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="26" t="str">
+        <x:v>TEST-085</x:v>
+      </x:c>
+      <x:c r="B86" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C86" s="30" t="str">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="D86" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E86" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F86" s="30" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G86" s="30" t="str">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H86" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I86" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J86" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K86" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L86" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M86" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N86" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O86" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P86" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q86" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R86" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S86" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T86" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U86" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V86" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W86" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X86" s="30" t="str"/>
+      <x:c r="Y86" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z86" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA86" s="30" t="str">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="AB86" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC86" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="26" t="str">
+        <x:v>TEST-086</x:v>
+      </x:c>
+      <x:c r="B87" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C87" s="30" t="str">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="D87" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E87" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F87" s="30" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G87" s="30" t="str">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H87" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I87" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J87" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K87" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L87" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M87" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N87" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O87" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P87" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q87" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R87" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S87" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T87" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U87" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V87" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W87" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X87" s="30" t="str"/>
+      <x:c r="Y87" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z87" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA87" s="30" t="str">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="AB87" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC87" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="26" t="str">
+        <x:v>TEST-087</x:v>
+      </x:c>
+      <x:c r="B88" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C88" s="30" t="str">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="D88" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E88" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F88" s="30" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G88" s="30" t="str">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H88" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I88" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J88" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K88" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L88" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M88" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N88" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O88" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P88" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q88" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R88" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S88" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T88" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U88" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V88" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W88" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X88" s="30" t="str"/>
+      <x:c r="Y88" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z88" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA88" s="30" t="str">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="AB88" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC88" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="26" t="str">
+        <x:v>TEST-088</x:v>
+      </x:c>
+      <x:c r="B89" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C89" s="30" t="str">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="D89" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E89" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F89" s="30" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G89" s="30" t="str">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H89" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I89" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J89" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K89" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L89" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M89" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N89" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O89" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P89" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q89" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R89" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S89" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T89" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U89" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V89" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W89" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X89" s="30" t="str"/>
+      <x:c r="Y89" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z89" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA89" s="30" t="str">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="AB89" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC89" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="26" t="str">
+        <x:v>TEST-089</x:v>
+      </x:c>
+      <x:c r="B90" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C90" s="30" t="str">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="D90" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E90" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F90" s="30" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G90" s="30" t="str">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H90" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I90" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J90" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K90" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L90" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M90" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N90" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O90" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P90" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q90" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R90" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S90" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T90" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U90" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V90" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W90" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X90" s="30" t="str"/>
+      <x:c r="Y90" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z90" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA90" s="30" t="str">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="AB90" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC90" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="26" t="str">
+        <x:v>TEST-090</x:v>
+      </x:c>
+      <x:c r="B91" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C91" s="30" t="str">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="D91" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E91" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F91" s="30" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G91" s="30" t="str">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H91" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I91" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J91" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K91" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L91" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M91" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N91" s="12" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O91" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P91" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q91" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R91" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S91" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T91" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U91" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V91" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W91" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X91" s="30" t="str"/>
+      <x:c r="Y91" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z91" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA91" s="30" t="str">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="AB91" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC91" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="26" t="str">
+        <x:v>TEST-091</x:v>
+      </x:c>
+      <x:c r="B92" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C92" s="30" t="str">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="D92" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E92" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F92" s="30" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G92" s="30" t="str">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H31" s="31" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I31" s="31" t="str">
+      <x:c r="H92" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I92" s="30" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J31" s="31" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K31" s="31" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L31" s="31" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M31" s="15" t="str">
-        <x:v>BB</x:v>
-      </x:c>
-      <x:c r="N31" s="15" t="str">
+      <x:c r="J92" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K92" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L92" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M92" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N92" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O92" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P92" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q92" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R92" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S92" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T92" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U92" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V92" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W92" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X92" s="30" t="str"/>
+      <x:c r="Y92" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z92" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA92" s="30" t="str">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="AB92" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC92" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="26" t="str">
+        <x:v>TEST-092</x:v>
+      </x:c>
+      <x:c r="B93" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C93" s="30" t="str">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="D93" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E93" s="30" t="str">
+        <x:v>October</x:v>
+      </x:c>
+      <x:c r="F93" s="30" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G93" s="30" t="str">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H93" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I93" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K93" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L93" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M93" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N93" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O93" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P93" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q93" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R93" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S93" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T93" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U93" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V93" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W93" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X93" s="30" t="str"/>
+      <x:c r="Y93" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z93" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA93" s="30" t="str">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="AB93" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC93" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="26" t="str">
+        <x:v>TEST-093</x:v>
+      </x:c>
+      <x:c r="B94" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C94" s="30" t="str">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="D94" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E94" s="30" t="str">
+        <x:v>November</x:v>
+      </x:c>
+      <x:c r="F94" s="30" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G94" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H94" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I94" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J94" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K94" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L94" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M94" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N94" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O94" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P94" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q94" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R94" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S94" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T94" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U94" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V94" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W94" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X94" s="30" t="str"/>
+      <x:c r="Y94" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z94" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA94" s="30" t="str">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="AB94" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC94" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="26" t="str">
+        <x:v>TEST-094</x:v>
+      </x:c>
+      <x:c r="B95" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C95" s="30" t="str">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="D95" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E95" s="30" t="str">
+        <x:v>November</x:v>
+      </x:c>
+      <x:c r="F95" s="30" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G95" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H95" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I95" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J95" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K95" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L95" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M95" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N95" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O95" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P95" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q95" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R95" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S95" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T95" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U95" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V95" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W95" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X95" s="30" t="str"/>
+      <x:c r="Y95" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z95" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA95" s="30" t="str">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="AB95" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC95" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="26" t="str">
+        <x:v>TEST-095</x:v>
+      </x:c>
+      <x:c r="B96" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C96" s="30" t="str">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="D96" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E96" s="30" t="str">
+        <x:v>November</x:v>
+      </x:c>
+      <x:c r="F96" s="30" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G96" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H96" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I96" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K96" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L96" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M96" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N96" s="12" t="str">
         <x:v>DEU</x:v>
       </x:c>
-      <x:c r="O31" s="15" t="str">
+      <x:c r="O96" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P96" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q96" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R96" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S96" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T96" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U96" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V96" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W96" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X96" s="30" t="str"/>
+      <x:c r="Y96" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z96" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA96" s="30" t="str">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="AB96" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC96" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="26" t="str">
+        <x:v>TEST-096</x:v>
+      </x:c>
+      <x:c r="B97" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C97" s="30" t="str">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="D97" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E97" s="30" t="str">
+        <x:v>November</x:v>
+      </x:c>
+      <x:c r="F97" s="30" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G97" s="30" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H97" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I97" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J97" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K97" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L97" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M97" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N97" s="12" t="str">
+        <x:v>PRT</x:v>
+      </x:c>
+      <x:c r="O97" s="12" t="str">
         <x:v>Online TA</x:v>
       </x:c>
-      <x:c r="P31" s="15" t="str">
+      <x:c r="P97" s="12" t="str">
         <x:v>TA/TO</x:v>
       </x:c>
-      <x:c r="Q31" s="31" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R31" s="31" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S31" s="31" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T31" s="31" t="str">
+      <x:c r="Q97" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R97" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S97" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T97" s="30" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="U31" s="31" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="V31" s="31" t="str">
+      <x:c r="U97" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V97" s="30" t="str">
         <x:v>Non Refund</x:v>
       </x:c>
-      <x:c r="W31" s="31" t="str">
+      <x:c r="W97" s="30" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="X31" s="31" t="str"/>
-      <x:c r="Y31" s="31" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z31" s="15" t="str">
-        <x:v>Transient</x:v>
-      </x:c>
-      <x:c r="AA31" s="31" t="str">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="AB31" s="31" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC31" s="35" t="str">
+      <x:c r="X97" s="30" t="str"/>
+      <x:c r="Y97" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z97" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA97" s="30" t="str">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="AB97" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC97" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="26" t="str">
+        <x:v>TEST-097</x:v>
+      </x:c>
+      <x:c r="B98" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C98" s="30" t="str">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="D98" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E98" s="30" t="str">
+        <x:v>November</x:v>
+      </x:c>
+      <x:c r="F98" s="30" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G98" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H98" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I98" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J98" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K98" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L98" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M98" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N98" s="12" t="str">
+        <x:v>GBR</x:v>
+      </x:c>
+      <x:c r="O98" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P98" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q98" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R98" s="30" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S98" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T98" s="30" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="U98" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V98" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W98" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X98" s="30" t="str"/>
+      <x:c r="Y98" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z98" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA98" s="30" t="str">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="AB98" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC98" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="26" t="str">
+        <x:v>TEST-098</x:v>
+      </x:c>
+      <x:c r="B99" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C99" s="30" t="str">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="D99" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E99" s="30" t="str">
+        <x:v>November</x:v>
+      </x:c>
+      <x:c r="F99" s="30" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G99" s="30" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H99" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I99" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J99" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K99" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L99" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M99" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N99" s="12" t="str">
+        <x:v>FRA</x:v>
+      </x:c>
+      <x:c r="O99" s="12" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P99" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q99" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R99" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S99" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T99" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U99" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V99" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W99" s="30" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X99" s="30" t="str"/>
+      <x:c r="Y99" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z99" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA99" s="30" t="str">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="AB99" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC99" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="26" t="str">
+        <x:v>TEST-099</x:v>
+      </x:c>
+      <x:c r="B100" s="12" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C100" s="30" t="str">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="D100" s="30" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E100" s="30" t="str">
+        <x:v>November</x:v>
+      </x:c>
+      <x:c r="F100" s="30" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G100" s="30" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H100" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I100" s="30" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J100" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K100" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L100" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M100" s="12" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N100" s="12" t="str">
+        <x:v>ESP</x:v>
+      </x:c>
+      <x:c r="O100" s="12" t="str">
+        <x:v>Groups</x:v>
+      </x:c>
+      <x:c r="P100" s="12" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q100" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R100" s="30" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S100" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T100" s="30" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U100" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V100" s="30" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W100" s="30" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X100" s="30" t="str"/>
+      <x:c r="Y100" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z100" s="12" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA100" s="30" t="str">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="AB100" s="30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC100" s="34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="27" t="str">
+        <x:v>TEST-100</x:v>
+      </x:c>
+      <x:c r="B101" s="15" t="str">
+        <x:v>City Hotel</x:v>
+      </x:c>
+      <x:c r="C101" s="31" t="str">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="D101" s="31" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="E101" s="31" t="str">
+        <x:v>November</x:v>
+      </x:c>
+      <x:c r="F101" s="31" t="str">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G101" s="31" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H101" s="31" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I101" s="31" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J101" s="31" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K101" s="31" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L101" s="31" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M101" s="15" t="str">
+        <x:v>BB</x:v>
+      </x:c>
+      <x:c r="N101" s="15" t="str">
+        <x:v>DEU</x:v>
+      </x:c>
+      <x:c r="O101" s="15" t="str">
+        <x:v>Online TA</x:v>
+      </x:c>
+      <x:c r="P101" s="15" t="str">
+        <x:v>TA/TO</x:v>
+      </x:c>
+      <x:c r="Q101" s="31" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R101" s="31" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S101" s="31" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T101" s="31" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="U101" s="31" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V101" s="31" t="str">
+        <x:v>Non Refund</x:v>
+      </x:c>
+      <x:c r="W101" s="31" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X101" s="31" t="str"/>
+      <x:c r="Y101" s="31" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z101" s="15" t="str">
+        <x:v>Transient</x:v>
+      </x:c>
+      <x:c r="AA101" s="31" t="str">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="AB101" s="31" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC101" s="35" t="str">
         <x:v>0</x:v>
       </x:c>
     </x:row>
